--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T07:40:29+00:00</t>
+    <t>2026-08-24T13:49:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/DiagnosticReport|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/DiagnosticReport</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -1506,7 +1506,7 @@
     <t>QuelleKlinischesBezugsdatum</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-labor/StructureDefinition/QuelleKlinischesBezugsdatum|2027.0.0}
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-labor/StructureDefinition/QuelleKlinischesBezugsdatum}
 </t>
   </si>
   <si>
@@ -2184,7 +2184,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="109.5390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="105.24609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:49:26+00:00</t>
+    <t>2026-08-28T09:59:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:59:02+00:00</t>
+    <t>2026-08-28T10:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:19:24+00:00</t>
+    <t>2026-09-01T07:28:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T07:28:55+00:00</t>
+    <t>2026-09-01T08:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:17:52+00:00</t>
+    <t>2026-09-01T11:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:26:20+00:00</t>
+    <t>2026-09-01T11:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:37:07+00:00</t>
+    <t>2026-09-01T11:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:44:40+00:00</t>
+    <t>2026-09-01T12:05:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:05:15+00:00</t>
+    <t>2026-09-01T12:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:12:27+00:00</t>
+    <t>2026-09-01T12:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:31:59+00:00</t>
+    <t>2026-09-01T12:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:37:11+00:00</t>
+    <t>2026-09-01T12:41:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:41:57+00:00</t>
+    <t>2026-09-01T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:58:26+00:00</t>
+    <t>2026-09-01T13:38:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:38:20+00:00</t>
+    <t>2026-09-01T13:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:44:38+00:00</t>
+    <t>2026-09-01T14:35:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:35:41+00:00</t>
+    <t>2026-09-01T15:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:11:46+00:00</t>
+    <t>2026-09-01T15:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:27:37+00:00</t>
+    <t>2026-09-01T15:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:32:49+00:00</t>
+    <t>2026-09-01T15:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:38:53+00:00</t>
+    <t>2026-09-01T16:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:17:13+00:00</t>
+    <t>2026-09-01T16:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:23:29+00:00</t>
+    <t>2026-09-02T06:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:57:39+00:00</t>
+    <t>2026-09-02T07:24:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:24:40+00:00</t>
+    <t>2026-09-02T08:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T08:07:59+00:00</t>
+    <t>2026-09-02T09:10:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:10:52+00:00</t>
+    <t>2026-09-02T09:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:21:54+00:00</t>
+    <t>2026-09-02T10:32:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:32:32+00:00</t>
+    <t>2026-09-02T10:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:47:13+00:00</t>
+    <t>2026-09-02T11:41:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T11:41:16+00:00</t>
+    <t>2026-09-02T11:51:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
